--- a/Result/profitability/3494.xlsx
+++ b/Result/profitability/3494.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.32625</v>
+        <v>-0.345</v>
       </c>
       <c r="N2" t="n">
-        <v>16.5425</v>
+        <v>16.12875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.255</v>
+        <v>-0.2324999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>19.54375</v>
+        <v>19.0725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.12125</v>
+        <v>-0.1075</v>
       </c>
       <c r="N4" t="n">
-        <v>22.18</v>
+        <v>21.86625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.008749999999999966</v>
+        <v>-0.01499999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>24.5625</v>
+        <v>24.4775</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05750000000000004</v>
+        <v>0.09250000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>27.915</v>
+        <v>28.17875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1887500000000001</v>
+        <v>0.24625</v>
       </c>
       <c r="N7" t="n">
-        <v>30.39125</v>
+        <v>31.145</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3250000000000001</v>
+        <v>0.32875</v>
       </c>
       <c r="N8" t="n">
-        <v>34.01875</v>
+        <v>33.7625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.31</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="N9" t="n">
         <v>35.8175</v>
@@ -1899,7 +1899,7 @@
         <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="N12" t="n">
         <v>33.36875</v>
@@ -2026,7 +2026,7 @@
         <v>-0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="N13" t="n">
         <v>33.98625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>252</v>
+      </c>
+      <c r="D75" t="n">
+        <v>220</v>
+      </c>
+      <c r="E75" t="n">
+        <v>32</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3675</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.3225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1034482758620688</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.049999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.138047138047138</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.05000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05044510385756673</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
